--- a/設計/釣りMAP_テーブル設計.xlsx
+++ b/設計/釣りMAP_テーブル設計.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SerioFishingMap\設計\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FishingSiteMap\SerioFishingMap\設計\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A39CA6-8C81-4968-B544-406FA625B844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AFCD580-5650-489C-887D-DAE91305B92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="命名規則" sheetId="14" r:id="rId1"/>
@@ -41,12 +41,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="340">
   <si>
     <t>〇</t>
     <phoneticPr fontId="1"/>
@@ -1209,6 +1212,10 @@
   </si>
   <si>
     <t>ki</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>aaaaa</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1714,9 +1721,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0E7422-8CFB-444E-BF32-7DFDC2070A8C}">
   <dimension ref="B2:D35"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
-    <row r="2" spans="2:4" ht="30">
+    <row r="2" spans="2:4" ht="28.8">
       <c r="B2" s="14" t="s">
         <v>16</v>
       </c>
@@ -1907,10 +1914,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F1A6C79-C642-48F5-8BF8-B30990347762}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.625" customWidth="1"/>
+    <col min="3" max="3" width="21.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1966,10 +1973,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4FAC455-EBE5-45F0-AE45-FC4F50117C69}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.25" customWidth="1"/>
+    <col min="3" max="3" width="19.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2012,10 +2019,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{009770D1-115F-4855-AEFB-C03D3EED6C97}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="13.875" customWidth="1"/>
-    <col min="3" max="3" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.8984375" customWidth="1"/>
+    <col min="3" max="3" width="24.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2058,10 +2065,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{299DE3FB-EA4A-4DAF-8520-5AA42174CDE6}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2107,17 +2114,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1AD61BB-7A76-4386-BCD5-E9A18EDC3F40}">
-  <dimension ref="B2:H14"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="B2:H17"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="20.625" customWidth="1"/>
-    <col min="4" max="4" width="10.75" customWidth="1"/>
+    <col min="2" max="2" width="20.3984375" customWidth="1"/>
+    <col min="3" max="3" width="20.59765625" customWidth="1"/>
+    <col min="4" max="4" width="10.69921875" customWidth="1"/>
     <col min="5" max="5" width="10.5" customWidth="1"/>
-    <col min="6" max="6" width="11.25" customWidth="1"/>
-    <col min="7" max="7" width="12.75" customWidth="1"/>
-    <col min="8" max="8" width="18.125" customWidth="1"/>
+    <col min="6" max="6" width="11.19921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+    <col min="8" max="8" width="18.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
@@ -2327,24 +2334,30 @@
         <v>80</v>
       </c>
     </row>
+    <row r="17" spans="2:2">
+      <c r="B17" t="s">
+        <v>339</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{689F4B28-A447-469F-8B49-F93825F1A52C}">
   <dimension ref="B2:H8"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="21.875" customWidth="1"/>
-    <col min="3" max="3" width="20.625" customWidth="1"/>
-    <col min="4" max="4" width="10.75" customWidth="1"/>
+    <col min="2" max="2" width="21.8984375" customWidth="1"/>
+    <col min="3" max="3" width="20.59765625" customWidth="1"/>
+    <col min="4" max="4" width="10.69921875" customWidth="1"/>
     <col min="5" max="5" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="12.75" customWidth="1"/>
-    <col min="8" max="8" width="18.125" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+    <col min="8" max="8" width="18.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
@@ -2483,15 +2496,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDF4A4DA-D682-4B3C-A96B-E66C5527E65D}">
   <dimension ref="B2:T38"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="20.625" customWidth="1"/>
-    <col min="4" max="4" width="10.75" customWidth="1"/>
+    <col min="2" max="2" width="20.3984375" customWidth="1"/>
+    <col min="3" max="3" width="20.59765625" customWidth="1"/>
+    <col min="4" max="4" width="10.69921875" customWidth="1"/>
     <col min="5" max="5" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="12.75" customWidth="1"/>
-    <col min="8" max="8" width="18.125" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+    <col min="8" max="8" width="18.09765625" customWidth="1"/>
     <col min="11" max="11" width="14.5" customWidth="1"/>
     <col min="12" max="14" width="12" customWidth="1"/>
   </cols>
@@ -3253,14 +3266,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{090C3BA2-3F86-4CEC-BBAC-E721E52F27B1}">
   <dimension ref="B2:M30"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.25" customWidth="1"/>
+    <col min="3" max="3" width="24.09765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.19921875" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="17.375" customWidth="1"/>
-    <col min="13" max="14" width="12.25" customWidth="1"/>
+    <col min="12" max="12" width="17.3984375" customWidth="1"/>
+    <col min="13" max="14" width="12.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:13">
@@ -3604,11 +3617,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3441F138-C377-4DF2-880C-B63C6BCBC723}">
   <dimension ref="B3:G10"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.25" customWidth="1"/>
+    <col min="4" max="4" width="10.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:7">
@@ -3681,11 +3694,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D57ABB-7C93-41D8-9C0E-B0207E1A1C26}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="10.8984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3762,16 +3775,16 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B8CCEAB-3F5F-477B-AABF-B52A754FA6A1}">
   <dimension ref="B2:I25"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="5.375" customWidth="1"/>
-    <col min="2" max="2" width="16.625" customWidth="1"/>
-    <col min="3" max="3" width="22.75" customWidth="1"/>
+    <col min="1" max="1" width="5.3984375" customWidth="1"/>
+    <col min="2" max="2" width="16.59765625" customWidth="1"/>
+    <col min="3" max="3" width="22.69921875" customWidth="1"/>
     <col min="4" max="4" width="11.5" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="12.625" customWidth="1"/>
-    <col min="7" max="7" width="11.375" customWidth="1"/>
-    <col min="8" max="8" width="15.75" customWidth="1"/>
+    <col min="6" max="6" width="12.59765625" customWidth="1"/>
+    <col min="7" max="7" width="11.3984375" customWidth="1"/>
+    <col min="8" max="8" width="15.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
@@ -4066,13 +4079,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC5041F-FCFC-4E91-BBD7-37CA71CDB0C7}">
   <dimension ref="A1:L16"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="29.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.09765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">

--- a/設計/釣りMAP_テーブル設計.xlsx
+++ b/設計/釣りMAP_テーブル設計.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SerioFishingMap\設計\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FishingSiteMap\SerioFishingMap\設計\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A39CA6-8C81-4968-B544-406FA625B844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2CE4224-2988-4455-B048-23BB21606AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="命名規則" sheetId="14" r:id="rId1"/>
@@ -19,13 +19,12 @@
     <sheet name="釣果" sheetId="2" r:id="rId4"/>
     <sheet name="道具トラン" sheetId="17" r:id="rId5"/>
     <sheet name="仕掛けトラン" sheetId="10" r:id="rId6"/>
-    <sheet name="水質トラン" sheetId="12" r:id="rId7"/>
-    <sheet name="魚マスタ" sheetId="4" r:id="rId8"/>
-    <sheet name="釣場マスタ" sheetId="5" r:id="rId9"/>
-    <sheet name="メンバーマスタ" sheetId="6" r:id="rId10"/>
-    <sheet name="定数(釣り種別マスタ)" sheetId="7" r:id="rId11"/>
-    <sheet name="定数(道具マスタ)" sheetId="9" r:id="rId12"/>
-    <sheet name="定数(餌マスタ)" sheetId="11" r:id="rId13"/>
+    <sheet name="魚マスタ" sheetId="4" r:id="rId7"/>
+    <sheet name="釣場マスタ" sheetId="5" r:id="rId8"/>
+    <sheet name="メンバーマスタ" sheetId="6" r:id="rId9"/>
+    <sheet name="定数(釣り種別マスタ)" sheetId="7" r:id="rId10"/>
+    <sheet name="定数(道具マスタ)" sheetId="9" r:id="rId11"/>
+    <sheet name="定数(餌マスタ)" sheetId="11" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,12 +40,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="341">
   <si>
     <t>〇</t>
     <phoneticPr fontId="1"/>
@@ -91,9 +93,6 @@
     <t>ハリスの長さ</t>
   </si>
   <si>
-    <t>フックのサイズ</t>
-  </si>
-  <si>
     <t>ヒットパターン</t>
   </si>
   <si>
@@ -301,9 +300,6 @@
     <t>釣行に紐づくメンバー</t>
   </si>
   <si>
-    <t>釣行メンバーID</t>
-  </si>
-  <si>
     <t>FISHING_RESULT_ID</t>
   </si>
   <si>
@@ -370,15 +366,9 @@
     <t>竿の種類</t>
   </si>
   <si>
-    <t>仕掛け関連をまとめたテーブル。</t>
-  </si>
-  <si>
     <t>固定</t>
   </si>
   <si>
-    <t>仕掛けID（PK）</t>
-  </si>
-  <si>
     <t>説明</t>
   </si>
   <si>
@@ -388,27 +378,6 @@
     <t>これを書いてくださいをプレースホルダで</t>
   </si>
   <si>
-    <t>WaterCondition</t>
-  </si>
-  <si>
-    <t>水に関する環境データ。</t>
-  </si>
-  <si>
-    <t>このテーブルは最悪後回しでもよい</t>
-  </si>
-  <si>
-    <t>水質ID（PK）</t>
-  </si>
-  <si>
-    <t>透明度</t>
-  </si>
-  <si>
-    <t>塩分濃度</t>
-  </si>
-  <si>
-    <t>流れの強さ</t>
-  </si>
-  <si>
     <t>FISH</t>
   </si>
   <si>
@@ -430,42 +399,21 @@
     <t>string</t>
   </si>
   <si>
-    <t>魚目</t>
-  </si>
-  <si>
-    <t>分類</t>
-  </si>
-  <si>
     <t>Location</t>
   </si>
   <si>
     <t>釣り場のマスタ。</t>
   </si>
   <si>
-    <t>場所ID（PK）</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>座標（緯度経度）</t>
-  </si>
-  <si>
     <t>釣場タイプ（磯・船・堤防など）</t>
   </si>
   <si>
-    <t>快適性</t>
-  </si>
-  <si>
     <t>駐車場の有無</t>
   </si>
   <si>
     <t>bool</t>
   </si>
   <si>
-    <t>駐車場距離</t>
-  </si>
-  <si>
     <t>Member</t>
   </si>
   <si>
@@ -581,18 +529,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ROD_TYPE</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>REEL_TYPE</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>LINE_THICKNESS</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>LINE_TYPE</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -605,22 +545,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>WATER_QUALITY_ID</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>TRANSPARENCY</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>SALINITY</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CURRENT_STRENGTH</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>FISH_ID</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -629,14 +553,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>FISH_ORDER</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CATEGORY</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>LOCATION_ID</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -645,10 +561,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>COORDINATES</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>FISHING_SPOT_TYPE</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -661,19 +573,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>PARKING_DISTANCE</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>MEMBER_ID</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>EMPLOYEE_NUMBER</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>MEMBER_NAME</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -715,10 +619,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>TackleRecord</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>BIGINT</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -740,20 +640,6 @@
   </si>
   <si>
     <t>BOOLEAN</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>型</t>
-    <rPh sb="0" eb="1">
-      <t>カタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Null許容</t>
-    <rPh sb="4" eb="6">
-      <t>キョヨウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -780,10 +666,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>スピニングロッド</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>英名</t>
     <rPh sb="0" eb="2">
       <t>エイメイ</t>
@@ -798,29 +680,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Spining</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>BaitCasting</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>振出竿</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ベイトロッド</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>フライロッド</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Telescopic</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fly </t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1125,9 +984,6 @@
     <t>冬型の季節風。冷たい乾いた風。</t>
   </si>
   <si>
-    <t xml:space="preserve">RodType </t>
-  </si>
-  <si>
     <t xml:space="preserve">ReelType </t>
   </si>
   <si>
@@ -1209,6 +1065,251 @@
   </si>
   <si>
     <t>ki</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>道具</t>
+    <rPh sb="0" eb="2">
+      <t>ドウグ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>列挙型で不明を用意</t>
+  </si>
+  <si>
+    <t>仕掛け</t>
+    <rPh sb="0" eb="2">
+      <t>シカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rig</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕掛け関連をまとめたテーブル。</t>
+    <rPh sb="0" eb="2">
+      <t>シカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カンレン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フックのサイズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Location</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>釣り場マスタ</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>バ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>駐車場備考</t>
+    <rPh sb="3" eb="5">
+      <t>ビコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PARKING_DETAIL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>STRING</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>竿名</t>
+    <rPh sb="0" eb="1">
+      <t>サオ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ROD_NAME</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リール名</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リール号数</t>
+    <rPh sb="3" eb="5">
+      <t>ゴウスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>REEL_NAME</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リール種類</t>
+    <rPh sb="3" eb="5">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プルダウン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ライン号数</t>
+    <rPh sb="3" eb="5">
+      <t>ゴウスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ライン種類</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LINE_SIZE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>REEL_SIZE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>道具ID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仕掛けID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>料理向け</t>
+    <rPh sb="0" eb="2">
+      <t>リョウリ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>釣り情報向け</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>座標(緯度)</t>
+    <rPh sb="3" eb="5">
+      <t>イド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DECIMAL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>座標(経度)</t>
+    <rPh sb="3" eb="5">
+      <t>ケイド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LATITUDE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>快適性(トイレ有無、アクセス、人の多さ)</t>
+    <rPh sb="7" eb="9">
+      <t>ウム</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名称</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>場所ID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LONGITUDE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>釣行メンバーID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>釣行メンバーID</t>
+    <rPh sb="0" eb="2">
+      <t>チョウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>釣行メンバー</t>
+    <rPh sb="0" eb="2">
+      <t>チョウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メンバーID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メンバマスタ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>勤務地</t>
+    <rPh sb="0" eb="3">
+      <t>キンムチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LOCATION</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1216,7 +1317,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1261,15 +1362,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Yu Gothic"/>
@@ -1292,7 +1384,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1387,11 +1479,87 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1429,9 +1597,58 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1448,6 +1665,74 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1143000</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{380F6E4D-49E9-4254-B49B-6FFA19FD2DEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="358140"/>
+          <a:ext cx="2209800" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>なんの情報を持っておきたいか精査</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1714,11 +1999,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0E7422-8CFB-444E-BF32-7DFDC2070A8C}">
   <dimension ref="B2:D35"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
-    <row r="2" spans="2:4" ht="30">
+    <row r="2" spans="2:4" ht="28.8">
       <c r="B2" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="2:4">
@@ -1726,32 +2011,32 @@
         <v>1</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="D5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="D6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="D7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="D8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="2:4">
@@ -1759,52 +2044,52 @@
         <v>2</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="2:4">
       <c r="C10" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="C11" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="C12" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="D13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="D14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="2:4">
       <c r="D15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="D16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="2:4">
       <c r="D17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="2:4">
       <c r="D18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -1812,52 +2097,52 @@
         <v>3</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="2:4">
       <c r="D20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="2:4">
       <c r="D21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="2:4">
       <c r="D22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="2:4">
       <c r="D23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="2:4">
       <c r="D24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="2:4">
       <c r="D25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="2:4">
       <c r="D26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="2:4">
       <c r="D27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="2:4">
       <c r="D28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="2:4">
@@ -1865,37 +2150,37 @@
         <v>4</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="2:4">
       <c r="D30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="2:4">
       <c r="D31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="2:4">
       <c r="D32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="4:4">
       <c r="D33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="4:4">
       <c r="D34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="4:4">
       <c r="D35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1905,56 +2190,43 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F1A6C79-C642-48F5-8BF8-B30990347762}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4FAC455-EBE5-45F0-AE45-FC4F50117C69}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.625" customWidth="1"/>
+    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="C3" t="s">
-        <v>200</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="C4" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="E5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="C6" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C7" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="B8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -1964,43 +2236,43 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4FAC455-EBE5-45F0-AE45-FC4F50117C69}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{009770D1-115F-4855-AEFB-C03D3EED6C97}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.25" customWidth="1"/>
+    <col min="2" max="2" width="13.8984375" customWidth="1"/>
+    <col min="3" max="3" width="24.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="C4" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="E5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="C7" t="s">
-        <v>202</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2010,92 +2282,46 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{009770D1-115F-4855-AEFB-C03D3EED6C97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{299DE3FB-EA4A-4DAF-8520-5AA42174CDE6}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="13.875" customWidth="1"/>
-    <col min="3" max="3" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="C4" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="E5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="C6" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="C7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{299DE3FB-EA4A-4DAF-8520-5AA42174CDE6}">
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="C4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="E5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="B6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="B7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C7" t="s">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2107,63 +2333,63 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1AD61BB-7A76-4386-BCD5-E9A18EDC3F40}">
-  <dimension ref="B2:H14"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="B2:H19"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="20.625" customWidth="1"/>
-    <col min="4" max="4" width="10.75" customWidth="1"/>
-    <col min="5" max="5" width="10.5" customWidth="1"/>
-    <col min="6" max="6" width="11.25" customWidth="1"/>
-    <col min="7" max="7" width="12.75" customWidth="1"/>
-    <col min="8" max="8" width="18.125" customWidth="1"/>
+    <col min="2" max="2" width="20.3984375" customWidth="1"/>
+    <col min="3" max="3" width="20.59765625" customWidth="1"/>
+    <col min="4" max="4" width="10.69921875" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="11.19921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+    <col min="8" max="8" width="18.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="6" t="s">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -2173,224 +2399,243 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="F5" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="G5" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="H5" s="11" t="s">
         <v>59</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>63</v>
+      <c r="E6" s="29"/>
+      <c r="F6" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>62</v>
       </c>
       <c r="H6" s="12"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="D7" s="12"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>63</v>
+      <c r="G7" s="30" t="s">
+        <v>62</v>
       </c>
       <c r="H7" s="12"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="D8" s="12"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>63</v>
+      <c r="G8" s="30" t="s">
+        <v>62</v>
       </c>
       <c r="H8" s="12"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>71</v>
-      </c>
       <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>63</v>
+      <c r="E9" s="29"/>
+      <c r="F9" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>62</v>
       </c>
       <c r="H9" s="12"/>
     </row>
     <row r="10" spans="2:8">
       <c r="B10" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>73</v>
-      </c>
       <c r="D10" s="12"/>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>63</v>
+      <c r="F10" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>62</v>
       </c>
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="2:8">
       <c r="B11" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="D11" s="12"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="30" t="s">
         <v>75</v>
-      </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>76</v>
       </c>
       <c r="H11" s="12"/>
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="G12" s="30"/>
+      <c r="H12" s="12"/>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="D13" s="12"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="12"/>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="H12" s="12"/>
-    </row>
-    <row r="13" spans="2:8">
-      <c r="B13" s="16" t="s">
+    </row>
+    <row r="19" spans="2:3">
+      <c r="C19" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8">
-      <c r="C14" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{689F4B28-A447-469F-8B49-F93825F1A52C}">
-  <dimension ref="B2:H8"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="B2:H7"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="21.875" customWidth="1"/>
-    <col min="3" max="3" width="20.625" customWidth="1"/>
-    <col min="4" max="4" width="10.75" customWidth="1"/>
-    <col min="5" max="5" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="12.75" customWidth="1"/>
-    <col min="8" max="8" width="18.125" customWidth="1"/>
+    <col min="2" max="2" width="21.8984375" customWidth="1"/>
+    <col min="3" max="3" width="20.59765625" customWidth="1"/>
+    <col min="4" max="4" width="10.69921875" customWidth="1"/>
+    <col min="5" max="5" width="13.09765625" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+    <col min="8" max="8" width="18.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -2400,79 +2645,66 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="F5" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="G5" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="H5" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="6" spans="2:8">
-      <c r="B6" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="B6" s="33" t="s">
+        <v>334</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H6" s="12"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="33"/>
     </row>
     <row r="7" spans="2:8">
-      <c r="B7" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7" s="12"/>
-    </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="12"/>
+      <c r="B7" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -2483,48 +2715,48 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDF4A4DA-D682-4B3C-A96B-E66C5527E65D}">
   <dimension ref="B2:T38"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="20.625" customWidth="1"/>
-    <col min="4" max="4" width="10.75" customWidth="1"/>
+    <col min="2" max="2" width="20.3984375" customWidth="1"/>
+    <col min="3" max="3" width="20.59765625" customWidth="1"/>
+    <col min="4" max="4" width="10.69921875" customWidth="1"/>
     <col min="5" max="5" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="12.75" customWidth="1"/>
-    <col min="8" max="8" width="18.125" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+    <col min="8" max="8" width="18.09765625" customWidth="1"/>
     <col min="11" max="11" width="14.5" customWidth="1"/>
     <col min="12" max="14" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14">
       <c r="B2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="K2" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="2:14">
       <c r="B3" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>5</v>
@@ -2533,39 +2765,39 @@
       <c r="E3" s="6"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
-      <c r="H3" s="8" t="s">
-        <v>52</v>
+      <c r="H3" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="K3" t="s">
-        <v>254</v>
+        <v>215</v>
       </c>
       <c r="L3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M3" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="N3" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="2:14">
       <c r="B4" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="3"/>
+        <v>52</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="27"/>
       <c r="L4" t="s">
-        <v>244</v>
+        <v>205</v>
       </c>
       <c r="M4" t="s">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -2573,31 +2805,31 @@
     </row>
     <row r="5" spans="2:14">
       <c r="B5" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="F5" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="G5" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="H5" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>60</v>
-      </c>
       <c r="L5" t="s">
-        <v>262</v>
+        <v>223</v>
       </c>
       <c r="M5" t="s">
-        <v>258</v>
+        <v>219</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -2605,25 +2837,25 @@
     </row>
     <row r="6" spans="2:14">
       <c r="B6" s="12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="L6" t="s">
-        <v>263</v>
+        <v>224</v>
       </c>
       <c r="M6" t="s">
-        <v>259</v>
+        <v>220</v>
       </c>
       <c r="N6">
         <v>2</v>
@@ -2631,25 +2863,25 @@
     </row>
     <row r="7" spans="2:14">
       <c r="B7" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
       <c r="L7" t="s">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="M7" t="s">
-        <v>260</v>
+        <v>221</v>
       </c>
       <c r="N7">
         <v>3</v>
@@ -2657,23 +2889,23 @@
     </row>
     <row r="8" spans="2:14">
       <c r="B8" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="L8" t="s">
-        <v>265</v>
+        <v>226</v>
       </c>
       <c r="M8" t="s">
-        <v>261</v>
+        <v>222</v>
       </c>
       <c r="N8">
         <v>4</v>
@@ -2681,52 +2913,52 @@
     </row>
     <row r="9" spans="2:14">
       <c r="B9" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
     </row>
     <row r="10" spans="2:14">
       <c r="B10" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="12"/>
       <c r="F10" s="12" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="2:14">
       <c r="B11" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="12"/>
       <c r="F11" s="12" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
       <c r="K11" t="s">
-        <v>255</v>
+        <v>216</v>
       </c>
       <c r="L11" t="s">
         <v>6</v>
@@ -2734,23 +2966,23 @@
     </row>
     <row r="12" spans="2:14">
       <c r="B12" s="12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
       <c r="F12" s="12" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="L12" t="s">
-        <v>244</v>
+        <v>205</v>
       </c>
       <c r="M12" t="s">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -2758,23 +2990,23 @@
     </row>
     <row r="13" spans="2:14">
       <c r="B13" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12"/>
       <c r="F13" s="12" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="L13" t="s">
-        <v>271</v>
+        <v>232</v>
       </c>
       <c r="M13" t="s">
-        <v>266</v>
+        <v>227</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -2782,23 +3014,23 @@
     </row>
     <row r="14" spans="2:14">
       <c r="B14" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="12"/>
       <c r="F14" s="12" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
       <c r="L14" t="s">
-        <v>272</v>
+        <v>233</v>
       </c>
       <c r="M14" t="s">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="N14">
         <v>2</v>
@@ -2806,23 +3038,23 @@
     </row>
     <row r="15" spans="2:14">
       <c r="B15" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
       <c r="F15" s="12" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="L15" t="s">
-        <v>273</v>
+        <v>234</v>
       </c>
       <c r="M15" t="s">
-        <v>268</v>
+        <v>229</v>
       </c>
       <c r="N15">
         <v>3</v>
@@ -2830,23 +3062,23 @@
     </row>
     <row r="16" spans="2:14">
       <c r="B16" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
       <c r="F16" s="12" t="s">
-        <v>212</v>
+        <v>182</v>
       </c>
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
       <c r="L16" t="s">
-        <v>295</v>
+        <v>256</v>
       </c>
       <c r="M16" t="s">
-        <v>269</v>
+        <v>230</v>
       </c>
       <c r="N16">
         <v>4</v>
@@ -2857,23 +3089,23 @@
         <v>2</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12" t="s">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
       <c r="I17" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L17" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="M17" t="s">
-        <v>270</v>
+        <v>231</v>
       </c>
       <c r="N17">
         <v>5</v>
@@ -2884,20 +3116,20 @@
         <v>4</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
       <c r="F18" s="12" t="s">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
       <c r="I18" t="s">
+        <v>185</v>
+      </c>
+      <c r="K18" t="s">
         <v>217</v>
-      </c>
-      <c r="K18" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="19" spans="2:20">
@@ -2905,12 +3137,12 @@
         <v>8</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="G19" s="12"/>
       <c r="H19" s="12"/>
@@ -2923,20 +3155,20 @@
         <v>9</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="12"/>
       <c r="F20" s="12" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
       <c r="L20" t="s">
-        <v>244</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -2947,29 +3179,29 @@
         <v>10</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="D21" s="12"/>
       <c r="E21" s="12"/>
       <c r="F21" s="12" t="s">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="G21" s="12"/>
       <c r="H21" s="12"/>
       <c r="I21" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L21" t="s">
-        <v>296</v>
+        <v>257</v>
       </c>
       <c r="M21" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="N21">
         <v>1</v>
       </c>
       <c r="O21" t="s">
-        <v>304</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22" spans="2:20">
@@ -2977,26 +3209,26 @@
         <v>11</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
       <c r="L22" t="s">
-        <v>297</v>
+        <v>258</v>
       </c>
       <c r="M22" t="s">
-        <v>276</v>
+        <v>237</v>
       </c>
       <c r="N22">
         <v>2</v>
       </c>
       <c r="O22" t="s">
-        <v>305</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23" spans="2:20">
@@ -3004,164 +3236,164 @@
         <v>12</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
       <c r="F23" s="12" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="G23" s="12"/>
       <c r="H23" s="12"/>
       <c r="L23" t="s">
-        <v>298</v>
+        <v>259</v>
       </c>
       <c r="M23" t="s">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c r="N23">
         <v>3</v>
       </c>
       <c r="O23" t="s">
-        <v>306</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24" spans="2:20">
       <c r="B24" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
       <c r="F24" s="12" t="s">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="G24" s="12"/>
       <c r="H24" s="12"/>
       <c r="I24" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L24" t="s">
-        <v>299</v>
+        <v>260</v>
       </c>
       <c r="M24" t="s">
-        <v>278</v>
+        <v>239</v>
       </c>
       <c r="N24">
         <v>4</v>
       </c>
       <c r="O24" t="s">
-        <v>307</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="2:20">
       <c r="B25" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="G25" s="12" t="s">
         <v>0</v>
       </c>
       <c r="H25" s="12"/>
       <c r="L25" t="s">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="M25" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25" t="s">
-        <v>308</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" spans="2:20">
       <c r="B26" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="12"/>
       <c r="F26" s="12" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="G26" s="12"/>
       <c r="H26" s="12"/>
       <c r="L26" t="s">
-        <v>301</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s">
-        <v>280</v>
+        <v>241</v>
       </c>
       <c r="N26">
         <v>6</v>
       </c>
       <c r="O26" t="s">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="T26" t="s">
-        <v>338</v>
+        <v>298</v>
       </c>
     </row>
     <row r="27" spans="2:20">
       <c r="B27" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="12"/>
       <c r="F27" s="12" t="s">
-        <v>214</v>
+        <v>184</v>
       </c>
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
       <c r="L27" t="s">
-        <v>302</v>
+        <v>263</v>
       </c>
       <c r="M27" t="s">
-        <v>281</v>
+        <v>242</v>
       </c>
       <c r="N27">
         <v>7</v>
       </c>
       <c r="O27" t="s">
-        <v>310</v>
+        <v>271</v>
       </c>
     </row>
     <row r="28" spans="2:20">
       <c r="L28" t="s">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="M28" t="s">
-        <v>282</v>
+        <v>243</v>
       </c>
       <c r="N28">
         <v>8</v>
       </c>
       <c r="O28" t="s">
-        <v>311</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="2:20">
       <c r="L29" t="s">
-        <v>284</v>
+        <v>245</v>
       </c>
       <c r="M29" t="s">
-        <v>283</v>
+        <v>244</v>
       </c>
       <c r="N29">
         <v>9</v>
@@ -3169,20 +3401,20 @@
     </row>
     <row r="31" spans="2:20">
       <c r="K31" t="s">
-        <v>257</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="2:20">
       <c r="L32" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="12:14">
       <c r="L33" t="s">
-        <v>244</v>
+        <v>205</v>
       </c>
       <c r="M33" t="s">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -3190,10 +3422,10 @@
     </row>
     <row r="34" spans="12:14">
       <c r="L34" t="s">
-        <v>285</v>
+        <v>246</v>
       </c>
       <c r="M34" t="s">
-        <v>290</v>
+        <v>251</v>
       </c>
       <c r="N34">
         <v>1</v>
@@ -3201,10 +3433,10 @@
     </row>
     <row r="35" spans="12:14">
       <c r="L35" t="s">
-        <v>286</v>
+        <v>247</v>
       </c>
       <c r="M35" t="s">
-        <v>291</v>
+        <v>252</v>
       </c>
       <c r="N35">
         <v>2</v>
@@ -3212,10 +3444,10 @@
     </row>
     <row r="36" spans="12:14">
       <c r="L36" t="s">
-        <v>287</v>
+        <v>248</v>
       </c>
       <c r="M36" t="s">
-        <v>292</v>
+        <v>253</v>
       </c>
       <c r="N36">
         <v>3</v>
@@ -3223,10 +3455,10 @@
     </row>
     <row r="37" spans="12:14">
       <c r="L37" t="s">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="M37" t="s">
-        <v>293</v>
+        <v>254</v>
       </c>
       <c r="N37">
         <v>4</v>
@@ -3234,16 +3466,19 @@
     </row>
     <row r="38" spans="12:14">
       <c r="L38" t="s">
-        <v>289</v>
+        <v>250</v>
       </c>
       <c r="M38" t="s">
-        <v>294</v>
+        <v>255</v>
       </c>
       <c r="N38">
         <v>5</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C4:H4"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3252,349 +3487,455 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{090C3BA2-3F86-4CEC-BBAC-E721E52F27B1}">
-  <dimension ref="B2:M30"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="B2:N26"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.25" customWidth="1"/>
+    <col min="3" max="3" width="22.69921875" customWidth="1"/>
+    <col min="8" max="8" width="15.8984375" customWidth="1"/>
+    <col min="9" max="10" width="12.19921875" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="17.375" customWidth="1"/>
-    <col min="13" max="14" width="12.25" customWidth="1"/>
+    <col min="12" max="12" width="17.3984375" customWidth="1"/>
+    <col min="13" max="14" width="12.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13">
-      <c r="J2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13">
-      <c r="B3" t="s">
+    <row r="2" spans="2:14">
+      <c r="K2" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+    </row>
+    <row r="3" spans="2:14">
+      <c r="B3" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+    </row>
+    <row r="4" spans="2:14">
+      <c r="B4" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+    </row>
+    <row r="5" spans="2:14">
+      <c r="B5" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="27"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+    </row>
+    <row r="6" spans="2:14">
+      <c r="B6" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+    </row>
+    <row r="7" spans="2:14">
+      <c r="B7" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="22"/>
+      <c r="F7" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="22"/>
+      <c r="K7" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+    </row>
+    <row r="8" spans="2:14">
+      <c r="B8" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="H8" s="22"/>
+      <c r="I8" t="s">
+        <v>301</v>
+      </c>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="N8" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
+      <c r="B9" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="H9" s="22"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="N9" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
+      <c r="B10" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="22"/>
+      <c r="I10" t="s">
+        <v>317</v>
+      </c>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="N10" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14">
+      <c r="B11" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="22"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="N11" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14">
+      <c r="B12" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="22"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="N12" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
+      <c r="B13" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="22"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+    </row>
+    <row r="14" spans="2:14">
+      <c r="K14" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+    </row>
+    <row r="15" spans="2:14">
+      <c r="K15" s="19"/>
+      <c r="L15" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="N15" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14">
+      <c r="K16" s="19"/>
+      <c r="L16" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="M16" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="N16" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="11:14">
+      <c r="K17" s="19"/>
+      <c r="L17" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="M17" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="N17" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="11:14">
+      <c r="K18" s="19"/>
+      <c r="L18" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="N18" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="11:14">
+      <c r="K19" s="19"/>
+      <c r="L19" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="M19" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="N19" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="11:14">
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+    </row>
+    <row r="21" spans="11:14">
+      <c r="K21" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+    </row>
+    <row r="22" spans="11:14">
+      <c r="K22" s="19"/>
+      <c r="L22" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="M22" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="N22" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="11:14">
+      <c r="K23" s="19"/>
+      <c r="L23" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="M23" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="J3" t="s">
-        <v>312</v>
-      </c>
-      <c r="K3" t="s">
-        <v>106</v>
-      </c>
-      <c r="L3" t="s">
-        <v>220</v>
-      </c>
-      <c r="M3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13">
-      <c r="C4" t="s">
-        <v>104</v>
-      </c>
-      <c r="K4" t="s">
-        <v>244</v>
-      </c>
-      <c r="L4" t="s">
-        <v>245</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13">
-      <c r="B5" s="17"/>
-      <c r="D5" t="s">
-        <v>215</v>
-      </c>
-      <c r="E5" t="s">
-        <v>216</v>
-      </c>
-      <c r="K5" t="s">
-        <v>219</v>
-      </c>
-      <c r="L5" t="s">
-        <v>222</v>
-      </c>
-      <c r="M5">
+      <c r="N23" s="19">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:13">
-      <c r="B6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D6" t="s">
+    <row r="24" spans="11:14">
+      <c r="K24" s="19"/>
+      <c r="L24" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="M24" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="N24" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="11:14">
+      <c r="K25" s="19"/>
+      <c r="L25" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="M25" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="K6" t="s">
-        <v>225</v>
-      </c>
-      <c r="L6" t="s">
-        <v>223</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13">
-      <c r="B7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" t="s">
-        <v>176</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="N25" s="19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="11:14">
+      <c r="K26" s="19"/>
+      <c r="L26" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="G7" t="s">
-        <v>217</v>
-      </c>
-      <c r="K7" t="s">
-        <v>224</v>
-      </c>
-      <c r="L7" t="s">
-        <v>227</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13">
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>177</v>
-      </c>
-      <c r="D8" t="s">
-        <v>213</v>
-      </c>
-      <c r="K8" t="s">
-        <v>226</v>
-      </c>
-      <c r="L8" t="s">
-        <v>228</v>
-      </c>
-      <c r="M8">
+      <c r="M26" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="N26" s="19">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:13">
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>178</v>
-      </c>
-      <c r="D9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E9" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13">
-      <c r="B10" t="s">
-        <v>147</v>
-      </c>
-      <c r="C10" t="s">
-        <v>179</v>
-      </c>
-      <c r="D10" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13">
-      <c r="J11" t="s">
-        <v>313</v>
-      </c>
-      <c r="K11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13">
-      <c r="K12" t="s">
-        <v>244</v>
-      </c>
-      <c r="L12" t="s">
-        <v>245</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13">
-      <c r="K13" t="s">
-        <v>232</v>
-      </c>
-      <c r="L13" t="s">
-        <v>229</v>
-      </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13">
-      <c r="K14" t="s">
-        <v>233</v>
-      </c>
-      <c r="L14" t="s">
-        <v>230</v>
-      </c>
-      <c r="M14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13">
-      <c r="K15" t="s">
-        <v>234</v>
-      </c>
-      <c r="L15" t="s">
-        <v>228</v>
-      </c>
-      <c r="M15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13">
-      <c r="K16" t="s">
-        <v>235</v>
-      </c>
-      <c r="L16" t="s">
-        <v>231</v>
-      </c>
-      <c r="M16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="10:13">
-      <c r="J18" t="s">
-        <v>314</v>
-      </c>
-      <c r="K18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="10:13">
-      <c r="K19" t="s">
-        <v>244</v>
-      </c>
-      <c r="L19" t="s">
-        <v>245</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="10:13">
-      <c r="K20" t="s">
-        <v>240</v>
-      </c>
-      <c r="L20" t="s">
-        <v>236</v>
-      </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="10:13">
-      <c r="K21" t="s">
-        <v>241</v>
-      </c>
-      <c r="L21" t="s">
-        <v>237</v>
-      </c>
-      <c r="M21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="10:13">
-      <c r="K22" t="s">
-        <v>242</v>
-      </c>
-      <c r="L22" t="s">
-        <v>238</v>
-      </c>
-      <c r="M22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="10:13">
-      <c r="K23" t="s">
-        <v>243</v>
-      </c>
-      <c r="L23" t="s">
-        <v>239</v>
-      </c>
-      <c r="M23">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="10:13">
-      <c r="J25" t="s">
-        <v>315</v>
-      </c>
-      <c r="K25" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="26" spans="10:13">
-      <c r="K26" t="s">
-        <v>244</v>
-      </c>
-      <c r="L26" t="s">
-        <v>245</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="10:13">
-      <c r="K27" t="s">
-        <v>250</v>
-      </c>
-      <c r="L27" t="s">
-        <v>246</v>
-      </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="10:13">
-      <c r="K28" t="s">
-        <v>251</v>
-      </c>
-      <c r="L28" t="s">
-        <v>247</v>
-      </c>
-      <c r="M28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="10:13">
-      <c r="K29" t="s">
-        <v>253</v>
-      </c>
-      <c r="L29" t="s">
-        <v>248</v>
-      </c>
-      <c r="M29">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="10:13">
-      <c r="K30" t="s">
-        <v>252</v>
-      </c>
-      <c r="L30" t="s">
-        <v>249</v>
-      </c>
-      <c r="M30">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C5:H5"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3603,221 +3944,212 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3441F138-C377-4DF2-880C-B63C6BCBC723}">
-  <dimension ref="B3:G10"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="B3:P11"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.25" customWidth="1"/>
+    <col min="3" max="3" width="18.59765625" customWidth="1"/>
+    <col min="4" max="4" width="10.19921875" customWidth="1"/>
+    <col min="8" max="8" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7">
-      <c r="B3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7">
-      <c r="D4" t="s">
+    <row r="3" spans="2:16">
+      <c r="B3" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16">
+      <c r="B4" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16">
+      <c r="B5" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="27"/>
+    </row>
+    <row r="6" spans="2:16">
+      <c r="B6" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16">
+      <c r="B7" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="22"/>
+      <c r="F7" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="22"/>
+    </row>
+    <row r="8" spans="2:16">
+      <c r="B8" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" s="22"/>
+      <c r="I8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16">
+      <c r="I9" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="5" spans="2:7">
-      <c r="D5" t="s">
-        <v>215</v>
-      </c>
-      <c r="E5" t="s">
-        <v>216</v>
-      </c>
-      <c r="F5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7">
-      <c r="B6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" t="s">
-        <v>180</v>
-      </c>
-      <c r="D6" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7">
-      <c r="B7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" t="s">
-        <v>181</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="G7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7">
-      <c r="G8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7">
-      <c r="G9" t="s">
+      <c r="P9" s="12"/>
+    </row>
+    <row r="10" spans="2:16">
+      <c r="I10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
-      <c r="G10" t="s">
-        <v>14</v>
+    <row r="11" spans="2:16">
+      <c r="I11" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C5:H5"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D57ABB-7C93-41D8-9C0E-B0207E1A1C26}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B8CCEAB-3F5F-477B-AABF-B52A754FA6A1}">
+  <dimension ref="B2:K8"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.875" customWidth="1"/>
+    <col min="1" max="1" width="5.3984375" customWidth="1"/>
+    <col min="2" max="2" width="16.59765625" customWidth="1"/>
+    <col min="3" max="3" width="22.69921875" customWidth="1"/>
+    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12.59765625" customWidth="1"/>
+    <col min="7" max="7" width="11.3984375" customWidth="1"/>
+    <col min="8" max="8" width="15.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="C4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="D5" t="s">
-        <v>215</v>
-      </c>
-      <c r="E5" t="s">
-        <v>216</v>
-      </c>
-      <c r="F5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="B6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" t="s">
-        <v>182</v>
-      </c>
-      <c r="D6" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="B7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" t="s">
-        <v>183</v>
-      </c>
-      <c r="D7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="B8" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="B9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" t="s">
-        <v>185</v>
-      </c>
-      <c r="D9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B8CCEAB-3F5F-477B-AABF-B52A754FA6A1}">
-  <dimension ref="B2:I25"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <cols>
-    <col min="1" max="1" width="5.375" customWidth="1"/>
-    <col min="2" max="2" width="16.625" customWidth="1"/>
-    <col min="3" max="3" width="22.75" customWidth="1"/>
-    <col min="4" max="4" width="11.5" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="12.625" customWidth="1"/>
-    <col min="7" max="7" width="11.375" customWidth="1"/>
-    <col min="8" max="8" width="15.75" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:9">
+    <row r="2" spans="2:11">
       <c r="B2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9">
+    </row>
+    <row r="3" spans="2:11">
       <c r="B3" s="6" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11">
+      <c r="B4" s="9" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="4" spans="2:9">
-      <c r="B4" s="9" t="s">
-        <v>53</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -3825,493 +4157,542 @@
       <c r="G4" s="2"/>
       <c r="H4" s="3"/>
       <c r="I4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11">
       <c r="B5" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="F5" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="G5" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="H5" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9">
+    </row>
+    <row r="6" spans="2:11">
       <c r="B6" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="2:9">
+    <row r="7" spans="2:11">
       <c r="B7" s="12" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
       <c r="F7" s="12" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
-    </row>
-    <row r="8" spans="2:9">
-      <c r="B8" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="C8" s="13" t="s">
+      <c r="K7" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11">
+      <c r="K8" t="s">
+        <v>325</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC5041F-FCFC-4E91-BBD7-37CA71CDB0C7}">
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="2" max="2" width="34.59765625" customWidth="1"/>
+    <col min="3" max="3" width="20.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.296875" customWidth="1"/>
+    <col min="8" max="8" width="15.5" customWidth="1"/>
+    <col min="9" max="9" width="16.09765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.09765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="B3" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="B4" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" t="s">
+        <v>286</v>
+      </c>
+      <c r="K4" t="s">
+        <v>187</v>
+      </c>
+      <c r="L4" t="s">
+        <v>297</v>
+      </c>
+      <c r="M4" t="s">
         <v>188</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-    </row>
-    <row r="9" spans="2:9">
-      <c r="B9" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-    </row>
-    <row r="10" spans="2:9">
-      <c r="B10" s="12"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-    </row>
-    <row r="11" spans="2:9">
-      <c r="B11" s="12"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-    </row>
-    <row r="12" spans="2:9">
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-    </row>
-    <row r="13" spans="2:9">
-      <c r="B13" s="12"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-    </row>
-    <row r="14" spans="2:9">
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-    </row>
-    <row r="15" spans="2:9">
-      <c r="B15" s="12"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-    </row>
-    <row r="16" spans="2:9">
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="12"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-    </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="12"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-    </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="12"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-    </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="12"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="12"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-    </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="12"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-    </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="12"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="B5" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="K5" t="s">
+        <v>206</v>
+      </c>
+      <c r="L5" t="s">
+        <v>205</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="B6" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" t="s">
+        <v>276</v>
+      </c>
+      <c r="L6" t="s">
+        <v>287</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="B7" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="22"/>
+      <c r="F7" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="K7" t="s">
+        <v>277</v>
+      </c>
+      <c r="L7" t="s">
+        <v>288</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="B8" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" t="s">
+        <v>115</v>
+      </c>
+      <c r="K8" t="s">
+        <v>278</v>
+      </c>
+      <c r="L8" t="s">
+        <v>289</v>
+      </c>
+      <c r="M8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="B9" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="31" t="s">
+        <v>327</v>
+      </c>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" t="s">
+        <v>113</v>
+      </c>
+      <c r="K9" t="s">
+        <v>279</v>
+      </c>
+      <c r="L9" t="s">
+        <v>290</v>
+      </c>
+      <c r="M9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="B10" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="31" t="s">
+        <v>327</v>
+      </c>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" t="s">
+        <v>113</v>
+      </c>
+      <c r="K10" t="s">
+        <v>280</v>
+      </c>
+      <c r="L10" t="s">
+        <v>291</v>
+      </c>
+      <c r="M10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="B11" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" t="s">
+        <v>113</v>
+      </c>
+      <c r="K11" t="s">
+        <v>281</v>
+      </c>
+      <c r="L11" t="s">
+        <v>292</v>
+      </c>
+      <c r="M11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="B12" s="19" t="s">
+        <v>330</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" t="s">
+        <v>115</v>
+      </c>
+      <c r="K12" t="s">
+        <v>282</v>
+      </c>
+      <c r="L12" t="s">
+        <v>293</v>
+      </c>
+      <c r="M12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="B13" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" t="s">
+        <v>120</v>
+      </c>
+      <c r="K13" t="s">
+        <v>283</v>
+      </c>
+      <c r="L13" t="s">
+        <v>294</v>
+      </c>
+      <c r="M13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="B14" s="19" t="s">
+        <v>308</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" t="s">
+        <v>113</v>
+      </c>
+      <c r="K14" t="s">
+        <v>284</v>
+      </c>
+      <c r="L14" t="s">
+        <v>295</v>
+      </c>
+      <c r="M14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="K15" t="s">
+        <v>285</v>
+      </c>
+      <c r="L15" t="s">
+        <v>296</v>
+      </c>
+      <c r="M15">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C5:H5"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC5041F-FCFC-4E91-BBD7-37CA71CDB0C7}">
-  <dimension ref="A1:L16"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F1A6C79-C642-48F5-8BF8-B30990347762}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="29.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="C3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="C4" t="s">
-        <v>130</v>
-      </c>
-      <c r="I4" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="D5" t="s">
-        <v>215</v>
-      </c>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="E5" t="s">
-        <v>216</v>
-      </c>
-      <c r="F5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="B6" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="I5" t="s">
-        <v>326</v>
-      </c>
-      <c r="J5" t="s">
-        <v>220</v>
-      </c>
-      <c r="K5" t="s">
-        <v>337</v>
-      </c>
-      <c r="L5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="B6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D6" t="s">
-        <v>209</v>
-      </c>
-      <c r="J6" t="s">
-        <v>245</v>
-      </c>
-      <c r="K6" t="s">
-        <v>244</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="B7" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7" t="s">
-        <v>191</v>
-      </c>
-      <c r="D7" s="18" t="s">
+      <c r="C6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="B7" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="B8" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="G8" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="F7" t="s">
-        <v>126</v>
-      </c>
-      <c r="J7" t="s">
-        <v>316</v>
-      </c>
-      <c r="K7" t="s">
-        <v>327</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="B8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" t="s">
-        <v>192</v>
-      </c>
-      <c r="D8" t="s">
-        <v>213</v>
-      </c>
-      <c r="F8" t="s">
-        <v>124</v>
-      </c>
-      <c r="J8" t="s">
-        <v>317</v>
-      </c>
-      <c r="K8" t="s">
-        <v>328</v>
-      </c>
-      <c r="L8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="B9" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="C9" t="s">
-        <v>193</v>
-      </c>
-      <c r="D9" t="s">
-        <v>213</v>
-      </c>
-      <c r="F9" t="s">
-        <v>124</v>
-      </c>
-      <c r="J9" t="s">
-        <v>318</v>
-      </c>
-      <c r="K9" t="s">
-        <v>329</v>
-      </c>
-      <c r="L9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="B10" t="s">
+      <c r="H8" s="22"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="C10" t="s">
-        <v>194</v>
-      </c>
-      <c r="D10" s="18" t="s">
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="F10" t="s">
-        <v>126</v>
-      </c>
-      <c r="J10" t="s">
-        <v>319</v>
-      </c>
-      <c r="K10" t="s">
-        <v>330</v>
-      </c>
-      <c r="L10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="B11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C11" t="s">
-        <v>195</v>
-      </c>
-      <c r="D11" t="s">
-        <v>214</v>
-      </c>
-      <c r="F11" t="s">
-        <v>137</v>
-      </c>
-      <c r="J11" t="s">
-        <v>320</v>
-      </c>
-      <c r="K11" t="s">
-        <v>331</v>
-      </c>
-      <c r="L11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="B12" t="s">
-        <v>138</v>
-      </c>
-      <c r="C12" t="s">
-        <v>196</v>
-      </c>
-      <c r="D12" t="s">
-        <v>209</v>
-      </c>
-      <c r="F12" t="s">
-        <v>124</v>
-      </c>
-      <c r="J12" t="s">
-        <v>321</v>
-      </c>
-      <c r="K12" t="s">
-        <v>332</v>
-      </c>
-      <c r="L12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="J13" t="s">
-        <v>322</v>
-      </c>
-      <c r="K13" t="s">
-        <v>333</v>
-      </c>
-      <c r="L13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="J14" t="s">
-        <v>323</v>
-      </c>
-      <c r="K14" t="s">
-        <v>334</v>
-      </c>
-      <c r="L14">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="J15" t="s">
-        <v>324</v>
-      </c>
-      <c r="K15" t="s">
-        <v>335</v>
-      </c>
-      <c r="L15">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="J16" t="s">
-        <v>325</v>
-      </c>
-      <c r="K16" t="s">
-        <v>336</v>
-      </c>
-      <c r="L16">
-        <v>10</v>
-      </c>
+      <c r="H9" s="22"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
